--- a/public/templates/PerkawinanAnak.xlsx
+++ b/public/templates/PerkawinanAnak.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0dccc67157c6ef23/文档/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECT WEB RANDIKA\sipandakabulan-new\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AAD2FDC-C70F-4CC5-A8BF-EB9F90A7DDF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D7AABCD-0396-45CC-B2B2-10BE73607978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{880B5ABD-AFFB-400F-A771-D5EC70E56583}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{880B5ABD-AFFB-400F-A771-D5EC70E56583}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -44,12 +42,6 @@
     <t>Sumber Data</t>
   </si>
   <si>
-    <t>Tahun 2021</t>
-  </si>
-  <si>
-    <t>Tahun 2022</t>
-  </si>
-  <si>
     <t xml:space="preserve">             Umur</t>
   </si>
   <si>
@@ -87,6 +79,12 @@
   </si>
   <si>
     <t>Pengadilan Agama</t>
+  </si>
+  <si>
+    <t>Tahun 2024</t>
+  </si>
+  <si>
+    <t>Tahun 2025</t>
   </si>
 </sst>
 </file>
@@ -321,7 +319,15 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -370,14 +376,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -717,144 +715,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F94A25-B1EC-478C-B406-B7BFDEA83A4D}">
   <dimension ref="B5:R13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="5" spans="2:18" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B5" s="20" t="s">
+    <row r="5" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B5" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="7" t="s">
+      <c r="D5" s="19"/>
+      <c r="E5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="12"/>
+    </row>
+    <row r="6" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="7"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7" t="s">
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="10"/>
+      <c r="L6" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="16" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="6" spans="2:18" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B6" s="20"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="7" t="s">
+    <row r="7" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="7"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="F7" s="8"/>
+      <c r="G7" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="14" t="s">
+      <c r="H7" s="8"/>
+      <c r="I7" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8" t="s">
         <v>5</v>
       </c>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="17"/>
     </row>
-    <row r="7" spans="2:18" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B7" s="20"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7" t="s">
+    <row r="8" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B8" s="7"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7" t="s">
+      <c r="F8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7" t="s">
+      <c r="G8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7" t="s">
+      <c r="H8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="15"/>
+      <c r="I8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="8"/>
+      <c r="L8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="R8" s="18"/>
     </row>
-    <row r="8" spans="2:18" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B8" s="20"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="K8" s="7"/>
-      <c r="L8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="R8" s="16"/>
-    </row>
-    <row r="9" spans="2:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>1</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="9"/>
+      <c r="C9" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="11"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
@@ -874,14 +872,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>2</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="9"/>
+      <c r="C10" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="11"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
@@ -901,14 +899,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>3</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="9"/>
+      <c r="C11" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="11"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -928,14 +926,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>4</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="9"/>
+      <c r="C12" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="11"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
@@ -955,14 +953,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B13" s="1">
         <v>5</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="9"/>
+      <c r="C13" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="11"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
@@ -984,13 +982,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="E5:K5"/>
-    <mergeCell ref="E6:J6"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="L5:R5"/>
@@ -1003,6 +994,13 @@
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C5:D8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="E5:K5"/>
+    <mergeCell ref="E6:J6"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
